--- a/data_lake/bart_temp_med/dt=2026-08-04/temperaturamed.xlsx
+++ b/data_lake/bart_temp_med/dt=2026-08-04/temperaturamed.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5EC0A6-7B8C-4673-9CD2-112E30E90937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC52B297-8C52-439F-9C50-F6F72881121D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DHIME!$A$1:$S$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$M$1:$M$212</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Temperatura!$B$4:$R$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -6353,8 +6354,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="121" width="32.42578125" style="50" customWidth="1"/>
-    <col min="122" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="122" width="32.42578125" style="50" customWidth="1"/>
+    <col min="123" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6643,7 +6644,9 @@
       <c r="L5" s="56">
         <v>29.2</v>
       </c>
-      <c r="M5" s="56"/>
+      <c r="M5" s="56">
+        <v>29.6</v>
+      </c>
       <c r="N5" s="56"/>
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
@@ -6674,7 +6677,7 @@
       <c r="AO5" s="56"/>
       <c r="AP5" s="58">
         <f t="shared" ref="AP5:AP68" si="0">COUNTIF(K5:AO5,"&gt;0")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ5" s="71" t="str">
         <f t="shared" ref="AQ5:AQ68" si="1">IF(AP5&gt;14,AVERAGE(K5:AO5),"")</f>
@@ -6726,7 +6729,9 @@
       <c r="L6" s="56">
         <v>29.2</v>
       </c>
-      <c r="M6" s="56"/>
+      <c r="M6" s="56">
+        <v>29.5</v>
+      </c>
       <c r="N6" s="56"/>
       <c r="O6" s="56"/>
       <c r="P6" s="56"/>
@@ -6757,7 +6762,7 @@
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ6" s="71" t="str">
         <f t="shared" si="1"/>
@@ -6809,7 +6814,9 @@
       <c r="L7" s="56">
         <v>32.1</v>
       </c>
-      <c r="M7" s="56"/>
+      <c r="M7" s="56">
+        <v>32.200000000000003</v>
+      </c>
       <c r="N7" s="56"/>
       <c r="O7" s="56"/>
       <c r="P7" s="56"/>
@@ -6840,7 +6847,7 @@
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ7" s="71" t="str">
         <f t="shared" si="1"/>
@@ -6892,7 +6899,9 @@
       <c r="L8" s="56">
         <v>29.8</v>
       </c>
-      <c r="M8" s="56"/>
+      <c r="M8" s="56">
+        <v>30.4</v>
+      </c>
       <c r="N8" s="56"/>
       <c r="O8" s="56"/>
       <c r="P8" s="56"/>
@@ -6923,7 +6932,7 @@
       <c r="AO8" s="56"/>
       <c r="AP8" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ8" s="71" t="str">
         <f t="shared" si="1"/>
@@ -6975,7 +6984,9 @@
       <c r="L9" s="56">
         <v>30.8</v>
       </c>
-      <c r="M9" s="56"/>
+      <c r="M9" s="56">
+        <v>30</v>
+      </c>
       <c r="N9" s="56"/>
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
@@ -7006,7 +7017,7 @@
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ9" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7058,7 +7069,9 @@
       <c r="L10" s="56">
         <v>34.1</v>
       </c>
-      <c r="M10" s="56"/>
+      <c r="M10" s="56">
+        <v>33.200000000000003</v>
+      </c>
       <c r="N10" s="56"/>
       <c r="O10" s="56"/>
       <c r="P10" s="56"/>
@@ -7089,7 +7102,7 @@
       <c r="AO10" s="56"/>
       <c r="AP10" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ10" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7141,7 +7154,9 @@
       <c r="L11" s="56">
         <v>34.700000000000003</v>
       </c>
-      <c r="M11" s="56"/>
+      <c r="M11" s="56">
+        <v>33.4</v>
+      </c>
       <c r="N11" s="56"/>
       <c r="O11" s="56"/>
       <c r="P11" s="56"/>
@@ -7172,7 +7187,7 @@
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ11" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7224,7 +7239,9 @@
       <c r="L12" s="56">
         <v>31.2</v>
       </c>
-      <c r="M12" s="56"/>
+      <c r="M12" s="56">
+        <v>30.8</v>
+      </c>
       <c r="N12" s="56"/>
       <c r="O12" s="56"/>
       <c r="P12" s="56"/>
@@ -7255,7 +7272,7 @@
       <c r="AO12" s="56"/>
       <c r="AP12" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ12" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7307,7 +7324,9 @@
       <c r="L13" s="56">
         <v>32.9</v>
       </c>
-      <c r="M13" s="56"/>
+      <c r="M13" s="56">
+        <v>31.2</v>
+      </c>
       <c r="N13" s="56"/>
       <c r="O13" s="56"/>
       <c r="P13" s="56"/>
@@ -7338,7 +7357,7 @@
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ13" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7390,7 +7409,9 @@
       <c r="L14" s="56">
         <v>26.1</v>
       </c>
-      <c r="M14" s="56"/>
+      <c r="M14" s="56">
+        <v>24.4</v>
+      </c>
       <c r="N14" s="56"/>
       <c r="O14" s="56"/>
       <c r="P14" s="56"/>
@@ -7421,7 +7442,7 @@
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ14" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7473,7 +7494,9 @@
       <c r="L15" s="56">
         <v>32</v>
       </c>
-      <c r="M15" s="56"/>
+      <c r="M15" s="56">
+        <v>30.1</v>
+      </c>
       <c r="N15" s="56"/>
       <c r="O15" s="56"/>
       <c r="P15" s="56"/>
@@ -7504,7 +7527,7 @@
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ15" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7556,7 +7579,9 @@
       <c r="L16" s="56">
         <v>29.1</v>
       </c>
-      <c r="M16" s="56"/>
+      <c r="M16" s="56">
+        <v>26.5</v>
+      </c>
       <c r="N16" s="56"/>
       <c r="O16" s="56"/>
       <c r="P16" s="56"/>
@@ -7587,7 +7612,7 @@
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ16" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7639,7 +7664,9 @@
       <c r="L17" s="56">
         <v>26</v>
       </c>
-      <c r="M17" s="56"/>
+      <c r="M17" s="56">
+        <v>25.7</v>
+      </c>
       <c r="N17" s="56"/>
       <c r="O17" s="56"/>
       <c r="P17" s="56"/>
@@ -7670,7 +7697,7 @@
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ17" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7722,7 +7749,9 @@
       <c r="L18" s="56">
         <v>19.5</v>
       </c>
-      <c r="M18" s="56"/>
+      <c r="M18" s="56">
+        <v>18.399999999999999</v>
+      </c>
       <c r="N18" s="56"/>
       <c r="O18" s="56"/>
       <c r="P18" s="56"/>
@@ -7753,7 +7782,7 @@
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ18" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7805,7 +7834,9 @@
       <c r="L19" s="56">
         <v>25.2</v>
       </c>
-      <c r="M19" s="56"/>
+      <c r="M19" s="56">
+        <v>23.9</v>
+      </c>
       <c r="N19" s="56"/>
       <c r="O19" s="56"/>
       <c r="P19" s="56"/>
@@ -7836,7 +7867,7 @@
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ19" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7888,7 +7919,9 @@
       <c r="L20" s="56">
         <v>24.8</v>
       </c>
-      <c r="M20" s="56"/>
+      <c r="M20" s="56">
+        <v>24.5</v>
+      </c>
       <c r="N20" s="56"/>
       <c r="O20" s="56"/>
       <c r="P20" s="56"/>
@@ -7919,7 +7952,7 @@
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ20" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7971,7 +8004,9 @@
       <c r="L21" s="56">
         <v>29.1</v>
       </c>
-      <c r="M21" s="56"/>
+      <c r="M21" s="56">
+        <v>28.6</v>
+      </c>
       <c r="N21" s="56"/>
       <c r="O21" s="56"/>
       <c r="P21" s="56"/>
@@ -8002,7 +8037,7 @@
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ21" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8054,7 +8089,9 @@
       <c r="L22" s="56">
         <v>15.2</v>
       </c>
-      <c r="M22" s="56"/>
+      <c r="M22" s="56">
+        <v>14.7</v>
+      </c>
       <c r="N22" s="56"/>
       <c r="O22" s="56"/>
       <c r="P22" s="56"/>
@@ -8085,7 +8122,7 @@
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ22" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8137,7 +8174,9 @@
       <c r="L23" s="56">
         <v>26.3</v>
       </c>
-      <c r="M23" s="56"/>
+      <c r="M23" s="56">
+        <v>25.5</v>
+      </c>
       <c r="N23" s="56"/>
       <c r="O23" s="56"/>
       <c r="P23" s="56"/>
@@ -8168,7 +8207,7 @@
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ23" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8220,7 +8259,9 @@
       <c r="L24" s="56">
         <v>32</v>
       </c>
-      <c r="M24" s="56"/>
+      <c r="M24" s="56">
+        <v>30.5</v>
+      </c>
       <c r="N24" s="56"/>
       <c r="O24" s="56"/>
       <c r="P24" s="56"/>
@@ -8251,7 +8292,7 @@
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ24" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8303,7 +8344,9 @@
       <c r="L25" s="56">
         <v>23.6</v>
       </c>
-      <c r="M25" s="56"/>
+      <c r="M25" s="56">
+        <v>23.1</v>
+      </c>
       <c r="N25" s="56"/>
       <c r="O25" s="56"/>
       <c r="P25" s="56"/>
@@ -8334,7 +8377,7 @@
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ25" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8386,7 +8429,9 @@
       <c r="L26" s="56">
         <v>11.8</v>
       </c>
-      <c r="M26" s="56"/>
+      <c r="M26" s="56">
+        <v>11.7</v>
+      </c>
       <c r="N26" s="56"/>
       <c r="O26" s="56"/>
       <c r="P26" s="56"/>
@@ -8417,7 +8462,7 @@
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ26" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8469,7 +8514,9 @@
       <c r="L27" s="56">
         <v>30.4</v>
       </c>
-      <c r="M27" s="56"/>
+      <c r="M27" s="56">
+        <v>27.5</v>
+      </c>
       <c r="N27" s="56"/>
       <c r="O27" s="56"/>
       <c r="P27" s="56"/>
@@ -8500,7 +8547,7 @@
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ27" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8552,7 +8599,9 @@
       <c r="L28" s="56">
         <v>29.7</v>
       </c>
-      <c r="M28" s="56"/>
+      <c r="M28" s="56">
+        <v>26.7</v>
+      </c>
       <c r="N28" s="56"/>
       <c r="O28" s="56"/>
       <c r="P28" s="56"/>
@@ -8583,7 +8632,7 @@
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ28" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8635,7 +8684,9 @@
       <c r="L29" s="56">
         <v>27.9</v>
       </c>
-      <c r="M29" s="56"/>
+      <c r="M29" s="56">
+        <v>28.3</v>
+      </c>
       <c r="N29" s="56"/>
       <c r="O29" s="56"/>
       <c r="P29" s="56"/>
@@ -8666,7 +8717,7 @@
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ29" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8718,7 +8769,9 @@
       <c r="L30" s="56">
         <v>27.3</v>
       </c>
-      <c r="M30" s="56"/>
+      <c r="M30" s="56">
+        <v>24.6</v>
+      </c>
       <c r="N30" s="56"/>
       <c r="O30" s="56"/>
       <c r="P30" s="56"/>
@@ -8749,7 +8802,7 @@
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ30" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8801,7 +8854,9 @@
       <c r="L31" s="98">
         <v>28.1</v>
       </c>
-      <c r="M31" s="98"/>
+      <c r="M31" s="98">
+        <v>28.1</v>
+      </c>
       <c r="N31" s="98"/>
       <c r="O31" s="98"/>
       <c r="P31" s="98"/>
@@ -8832,7 +8887,7 @@
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ31" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8884,7 +8939,9 @@
       <c r="L32" s="56">
         <v>19.733333333333331</v>
       </c>
-      <c r="M32" s="56"/>
+      <c r="M32" s="56">
+        <v>20.333333333333329</v>
+      </c>
       <c r="N32" s="56"/>
       <c r="O32" s="56"/>
       <c r="P32" s="56"/>
@@ -8915,7 +8972,7 @@
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ32" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8967,7 +9024,9 @@
       <c r="L33" s="56">
         <v>28.9</v>
       </c>
-      <c r="M33" s="56"/>
+      <c r="M33" s="56">
+        <v>26.45</v>
+      </c>
       <c r="N33" s="56"/>
       <c r="O33" s="56"/>
       <c r="P33" s="56"/>
@@ -8998,7 +9057,7 @@
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ33" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9050,7 +9109,9 @@
       <c r="L34" s="56">
         <v>21.4</v>
       </c>
-      <c r="M34" s="56"/>
+      <c r="M34" s="56">
+        <v>21.2</v>
+      </c>
       <c r="N34" s="56"/>
       <c r="O34" s="56"/>
       <c r="P34" s="56"/>
@@ -9081,7 +9142,7 @@
       <c r="AO34" s="56"/>
       <c r="AP34" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ34" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9133,7 +9194,9 @@
       <c r="L35" s="56">
         <v>23.8</v>
       </c>
-      <c r="M35" s="56"/>
+      <c r="M35" s="56">
+        <v>25.9</v>
+      </c>
       <c r="N35" s="56"/>
       <c r="O35" s="56"/>
       <c r="P35" s="56"/>
@@ -9164,7 +9227,7 @@
       <c r="AO35" s="56"/>
       <c r="AP35" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ35" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9297,7 +9360,9 @@
       <c r="L37" s="56">
         <v>26.85</v>
       </c>
-      <c r="M37" s="56"/>
+      <c r="M37" s="56">
+        <v>26.7</v>
+      </c>
       <c r="N37" s="56"/>
       <c r="O37" s="56"/>
       <c r="P37" s="56"/>
@@ -9328,7 +9393,7 @@
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ37" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9380,7 +9445,9 @@
       <c r="L38" s="56">
         <v>15.05</v>
       </c>
-      <c r="M38" s="56"/>
+      <c r="M38" s="56">
+        <v>16.149999999999999</v>
+      </c>
       <c r="N38" s="56"/>
       <c r="O38" s="56"/>
       <c r="P38" s="56"/>
@@ -9411,7 +9478,7 @@
       <c r="AO38" s="56"/>
       <c r="AP38" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ38" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9463,7 +9530,9 @@
       <c r="L39" s="56">
         <v>24</v>
       </c>
-      <c r="M39" s="56"/>
+      <c r="M39" s="56">
+        <v>23.06666666666667</v>
+      </c>
       <c r="N39" s="56"/>
       <c r="O39" s="56"/>
       <c r="P39" s="56"/>
@@ -9494,7 +9563,7 @@
       <c r="AO39" s="56"/>
       <c r="AP39" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ39" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9629,7 +9698,9 @@
       <c r="L41" s="56">
         <v>21.6</v>
       </c>
-      <c r="M41" s="56"/>
+      <c r="M41" s="56">
+        <v>21.266666666666669</v>
+      </c>
       <c r="N41" s="56"/>
       <c r="O41" s="56"/>
       <c r="P41" s="56"/>
@@ -9660,7 +9731,7 @@
       <c r="AO41" s="56"/>
       <c r="AP41" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ41" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9712,7 +9783,9 @@
       <c r="L42" s="56">
         <v>28.55</v>
       </c>
-      <c r="M42" s="56"/>
+      <c r="M42" s="56">
+        <v>28.25</v>
+      </c>
       <c r="N42" s="56"/>
       <c r="O42" s="56"/>
       <c r="P42" s="56"/>
@@ -9743,7 +9816,7 @@
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ42" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9792,8 +9865,12 @@
       <c r="K43" s="56">
         <v>31.15</v>
       </c>
-      <c r="L43" s="56"/>
-      <c r="M43" s="56"/>
+      <c r="L43" s="56">
+        <v>31</v>
+      </c>
+      <c r="M43" s="56">
+        <v>30.55</v>
+      </c>
       <c r="N43" s="56"/>
       <c r="O43" s="56"/>
       <c r="P43" s="56"/>
@@ -9824,7 +9901,7 @@
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ43" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9876,7 +9953,9 @@
       <c r="L44" s="56">
         <v>29.25</v>
       </c>
-      <c r="M44" s="56"/>
+      <c r="M44" s="56">
+        <v>27.225000000000001</v>
+      </c>
       <c r="N44" s="56"/>
       <c r="O44" s="56"/>
       <c r="P44" s="56"/>
@@ -9907,7 +9986,7 @@
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ44" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9959,7 +10038,9 @@
       <c r="L45" s="56">
         <v>29.7</v>
       </c>
-      <c r="M45" s="56"/>
+      <c r="M45" s="56">
+        <v>30.4</v>
+      </c>
       <c r="N45" s="56"/>
       <c r="O45" s="56"/>
       <c r="P45" s="56"/>
@@ -9990,7 +10071,7 @@
       <c r="AO45" s="56"/>
       <c r="AP45" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ45" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10042,7 +10123,9 @@
       <c r="L46" s="56">
         <v>29.45</v>
       </c>
-      <c r="M46" s="56"/>
+      <c r="M46" s="56">
+        <v>29.9</v>
+      </c>
       <c r="N46" s="56"/>
       <c r="O46" s="56"/>
       <c r="P46" s="56"/>
@@ -10073,7 +10156,7 @@
       <c r="AO46" s="56"/>
       <c r="AP46" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ46" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10125,7 +10208,9 @@
       <c r="L47" s="56">
         <v>30.966666666666669</v>
       </c>
-      <c r="M47" s="56"/>
+      <c r="M47" s="56">
+        <v>30.4</v>
+      </c>
       <c r="N47" s="56"/>
       <c r="O47" s="56"/>
       <c r="P47" s="56"/>
@@ -10156,7 +10241,7 @@
       <c r="AO47" s="56"/>
       <c r="AP47" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ47" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10366,7 +10451,9 @@
       <c r="L50" s="56">
         <v>30.55</v>
       </c>
-      <c r="M50" s="56"/>
+      <c r="M50" s="56">
+        <v>29.05</v>
+      </c>
       <c r="N50" s="56"/>
       <c r="O50" s="56"/>
       <c r="P50" s="56"/>
@@ -10397,7 +10484,7 @@
       <c r="AO50" s="56"/>
       <c r="AP50" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ50" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10607,7 +10694,9 @@
       <c r="L53" s="56">
         <v>29.85</v>
       </c>
-      <c r="M53" s="56"/>
+      <c r="M53" s="56">
+        <v>29.4</v>
+      </c>
       <c r="N53" s="56"/>
       <c r="O53" s="56"/>
       <c r="P53" s="56"/>
@@ -10638,7 +10727,7 @@
       <c r="AO53" s="56"/>
       <c r="AP53" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ53" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10690,7 +10779,9 @@
       <c r="L54" s="56">
         <v>30.75</v>
       </c>
-      <c r="M54" s="56"/>
+      <c r="M54" s="56">
+        <v>30.7</v>
+      </c>
       <c r="N54" s="56"/>
       <c r="O54" s="56"/>
       <c r="P54" s="56"/>
@@ -10721,7 +10812,7 @@
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ54" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10773,7 +10864,9 @@
       <c r="L55" s="56">
         <v>31.6</v>
       </c>
-      <c r="M55" s="56"/>
+      <c r="M55" s="56">
+        <v>28.65</v>
+      </c>
       <c r="N55" s="56"/>
       <c r="O55" s="56"/>
       <c r="P55" s="56"/>
@@ -10804,7 +10897,7 @@
       <c r="AO55" s="56"/>
       <c r="AP55" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ55" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10856,7 +10949,9 @@
       <c r="L56" s="56">
         <v>29.4</v>
       </c>
-      <c r="M56" s="56"/>
+      <c r="M56" s="56">
+        <v>29.2</v>
+      </c>
       <c r="N56" s="56"/>
       <c r="O56" s="56"/>
       <c r="P56" s="56"/>
@@ -10887,7 +10982,7 @@
       <c r="AO56" s="56"/>
       <c r="AP56" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ56" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11097,7 +11192,9 @@
       <c r="L59" s="56">
         <v>29.1</v>
       </c>
-      <c r="M59" s="56"/>
+      <c r="M59" s="56">
+        <v>29.6</v>
+      </c>
       <c r="N59" s="56"/>
       <c r="O59" s="56"/>
       <c r="P59" s="56"/>
@@ -11128,7 +11225,7 @@
       <c r="AO59" s="56"/>
       <c r="AP59" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ59" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11259,7 +11356,9 @@
       <c r="L61" s="56">
         <v>27.6</v>
       </c>
-      <c r="M61" s="56"/>
+      <c r="M61" s="56">
+        <v>26.3</v>
+      </c>
       <c r="N61" s="56"/>
       <c r="O61" s="56"/>
       <c r="P61" s="56"/>
@@ -11290,7 +11389,7 @@
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ61" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11342,7 +11441,9 @@
       <c r="L62" s="56">
         <v>27.533333333333331</v>
       </c>
-      <c r="M62" s="56"/>
+      <c r="M62" s="56">
+        <v>24.93333333333333</v>
+      </c>
       <c r="N62" s="56"/>
       <c r="O62" s="56"/>
       <c r="P62" s="56"/>
@@ -11373,7 +11474,7 @@
       <c r="AO62" s="56"/>
       <c r="AP62" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ62" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11664,7 +11765,9 @@
       <c r="L66" s="56">
         <v>27.65</v>
       </c>
-      <c r="M66" s="56"/>
+      <c r="M66" s="56">
+        <v>25.55</v>
+      </c>
       <c r="N66" s="56"/>
       <c r="O66" s="56"/>
       <c r="P66" s="56"/>
@@ -11695,7 +11798,7 @@
       <c r="AO66" s="56"/>
       <c r="AP66" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ66" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11747,7 +11850,9 @@
       <c r="L67" s="56">
         <v>28.2</v>
       </c>
-      <c r="M67" s="56"/>
+      <c r="M67" s="56">
+        <v>26.35</v>
+      </c>
       <c r="N67" s="56"/>
       <c r="O67" s="56"/>
       <c r="P67" s="56"/>
@@ -11778,7 +11883,7 @@
       <c r="AO67" s="56"/>
       <c r="AP67" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ67" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11830,7 +11935,9 @@
       <c r="L68" s="56">
         <v>26.55</v>
       </c>
-      <c r="M68" s="56"/>
+      <c r="M68" s="56">
+        <v>25</v>
+      </c>
       <c r="N68" s="56"/>
       <c r="O68" s="56"/>
       <c r="P68" s="56"/>
@@ -11861,7 +11968,7 @@
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ68" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11913,7 +12020,9 @@
       <c r="L69" s="56">
         <v>26.05</v>
       </c>
-      <c r="M69" s="56"/>
+      <c r="M69" s="56">
+        <v>24.8</v>
+      </c>
       <c r="N69" s="56"/>
       <c r="O69" s="56"/>
       <c r="P69" s="56"/>
@@ -11944,7 +12053,7 @@
       <c r="AO69" s="56"/>
       <c r="AP69" s="58">
         <f t="shared" ref="AP69:AP132" si="3">COUNTIF(K69:AO69,"&gt;0")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ69" s="71" t="str">
         <f t="shared" ref="AQ69:AQ132" si="4">IF(AP69&gt;14,AVERAGE(K69:AO69),"")</f>
@@ -11992,7 +12101,9 @@
       </c>
       <c r="K70" s="56"/>
       <c r="L70" s="56"/>
-      <c r="M70" s="56"/>
+      <c r="M70" s="56">
+        <v>26.06666666666667</v>
+      </c>
       <c r="N70" s="56"/>
       <c r="O70" s="56"/>
       <c r="P70" s="56"/>
@@ -12023,7 +12134,7 @@
       <c r="AO70" s="56"/>
       <c r="AP70" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ70" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12075,7 +12186,9 @@
       <c r="L71" s="56">
         <v>27</v>
       </c>
-      <c r="M71" s="56"/>
+      <c r="M71" s="56">
+        <v>26.63333333333334</v>
+      </c>
       <c r="N71" s="56"/>
       <c r="O71" s="56"/>
       <c r="P71" s="56"/>
@@ -12106,7 +12219,7 @@
       <c r="AO71" s="56"/>
       <c r="AP71" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ71" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12158,7 +12271,9 @@
       <c r="L72" s="56">
         <v>25.13333333333334</v>
       </c>
-      <c r="M72" s="56"/>
+      <c r="M72" s="56">
+        <v>25.466666666666669</v>
+      </c>
       <c r="N72" s="56"/>
       <c r="O72" s="56"/>
       <c r="P72" s="56"/>
@@ -12189,7 +12304,7 @@
       <c r="AO72" s="56"/>
       <c r="AP72" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ72" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12322,7 +12437,9 @@
       <c r="L74" s="56">
         <v>22.85</v>
       </c>
-      <c r="M74" s="56"/>
+      <c r="M74" s="56">
+        <v>20.3</v>
+      </c>
       <c r="N74" s="56"/>
       <c r="O74" s="56"/>
       <c r="P74" s="56"/>
@@ -12353,7 +12470,7 @@
       <c r="AO74" s="56"/>
       <c r="AP74" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ74" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12405,7 +12522,9 @@
       <c r="L75" s="56">
         <v>15.8</v>
       </c>
-      <c r="M75" s="56"/>
+      <c r="M75" s="56">
+        <v>15.4</v>
+      </c>
       <c r="N75" s="56"/>
       <c r="O75" s="56"/>
       <c r="P75" s="56"/>
@@ -12436,7 +12555,7 @@
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ75" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12488,7 +12607,9 @@
       <c r="L76" s="56">
         <v>21.65</v>
       </c>
-      <c r="M76" s="56"/>
+      <c r="M76" s="56">
+        <v>19.75</v>
+      </c>
       <c r="N76" s="56"/>
       <c r="O76" s="56"/>
       <c r="P76" s="56"/>
@@ -12519,7 +12640,7 @@
       <c r="AO76" s="56"/>
       <c r="AP76" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ76" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12571,7 +12692,9 @@
       <c r="L77" s="56">
         <v>25.333333333333329</v>
       </c>
-      <c r="M77" s="56"/>
+      <c r="M77" s="56">
+        <v>24</v>
+      </c>
       <c r="N77" s="56"/>
       <c r="O77" s="56"/>
       <c r="P77" s="56"/>
@@ -12602,7 +12725,7 @@
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ77" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12654,7 +12777,9 @@
       <c r="L78" s="56">
         <v>32.75</v>
       </c>
-      <c r="M78" s="56"/>
+      <c r="M78" s="56">
+        <v>31.65</v>
+      </c>
       <c r="N78" s="56"/>
       <c r="O78" s="56"/>
       <c r="P78" s="56"/>
@@ -12685,7 +12810,7 @@
       <c r="AO78" s="56"/>
       <c r="AP78" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ78" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12737,7 +12862,9 @@
       <c r="L79" s="56">
         <v>32.266666666666673</v>
       </c>
-      <c r="M79" s="56"/>
+      <c r="M79" s="56">
+        <v>31.466666666666669</v>
+      </c>
       <c r="N79" s="56"/>
       <c r="O79" s="56"/>
       <c r="P79" s="56"/>
@@ -12768,7 +12895,7 @@
       <c r="AO79" s="56"/>
       <c r="AP79" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ79" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12903,7 +13030,9 @@
       <c r="L81" s="56">
         <v>26.8</v>
       </c>
-      <c r="M81" s="56"/>
+      <c r="M81" s="56">
+        <v>23.7</v>
+      </c>
       <c r="N81" s="56"/>
       <c r="O81" s="56"/>
       <c r="P81" s="56"/>
@@ -12934,7 +13063,7 @@
       <c r="AO81" s="56"/>
       <c r="AP81" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ81" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12986,7 +13115,9 @@
       <c r="L82" s="56">
         <v>28</v>
       </c>
-      <c r="M82" s="56"/>
+      <c r="M82" s="56">
+        <v>25.333333333333329</v>
+      </c>
       <c r="N82" s="56"/>
       <c r="O82" s="56"/>
       <c r="P82" s="56"/>
@@ -13017,7 +13148,7 @@
       <c r="AO82" s="56"/>
       <c r="AP82" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ82" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13224,8 +13355,12 @@
       <c r="K85" s="56">
         <v>32.049999999999997</v>
       </c>
-      <c r="L85" s="56"/>
-      <c r="M85" s="56"/>
+      <c r="L85" s="56">
+        <v>32.85</v>
+      </c>
+      <c r="M85" s="56">
+        <v>32.15</v>
+      </c>
       <c r="N85" s="56"/>
       <c r="O85" s="56"/>
       <c r="P85" s="56"/>
@@ -13256,7 +13391,7 @@
       <c r="AO85" s="56"/>
       <c r="AP85" s="58">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ85" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13305,8 +13440,12 @@
       <c r="K86" s="56">
         <v>30.65</v>
       </c>
-      <c r="L86" s="56"/>
-      <c r="M86" s="56"/>
+      <c r="L86" s="56">
+        <v>31.2</v>
+      </c>
+      <c r="M86" s="56">
+        <v>30.45</v>
+      </c>
       <c r="N86" s="56"/>
       <c r="O86" s="56"/>
       <c r="P86" s="56"/>
@@ -13337,7 +13476,7 @@
       <c r="AO86" s="56"/>
       <c r="AP86" s="58">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ86" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13386,8 +13525,12 @@
       <c r="K87" s="56">
         <v>30.9</v>
       </c>
-      <c r="L87" s="56"/>
-      <c r="M87" s="56"/>
+      <c r="L87" s="56">
+        <v>32.15</v>
+      </c>
+      <c r="M87" s="56">
+        <v>32.225000000000001</v>
+      </c>
       <c r="N87" s="56"/>
       <c r="O87" s="56"/>
       <c r="P87" s="56"/>
@@ -13418,7 +13561,7 @@
       <c r="AO87" s="56"/>
       <c r="AP87" s="58">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ87" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13467,8 +13610,12 @@
       <c r="K88" s="56">
         <v>29.65</v>
       </c>
-      <c r="L88" s="56"/>
-      <c r="M88" s="56"/>
+      <c r="L88" s="56">
+        <v>31.5</v>
+      </c>
+      <c r="M88" s="56">
+        <v>31.3</v>
+      </c>
       <c r="N88" s="56"/>
       <c r="O88" s="56"/>
       <c r="P88" s="56"/>
@@ -13499,7 +13646,7 @@
       <c r="AO88" s="56"/>
       <c r="AP88" s="58">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ88" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13549,7 +13696,9 @@
         <v>31.4</v>
       </c>
       <c r="L89" s="56"/>
-      <c r="M89" s="56"/>
+      <c r="M89" s="56">
+        <v>33.75</v>
+      </c>
       <c r="N89" s="56"/>
       <c r="O89" s="56"/>
       <c r="P89" s="56"/>
@@ -13580,7 +13729,7 @@
       <c r="AO89" s="56"/>
       <c r="AP89" s="58">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ89" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13629,8 +13778,12 @@
       <c r="K90" s="56">
         <v>33.700000000000003</v>
       </c>
-      <c r="L90" s="56"/>
-      <c r="M90" s="56"/>
+      <c r="L90" s="56">
+        <v>33.1</v>
+      </c>
+      <c r="M90" s="56">
+        <v>32.400000000000013</v>
+      </c>
       <c r="N90" s="56"/>
       <c r="O90" s="56"/>
       <c r="P90" s="56"/>
@@ -13661,7 +13814,7 @@
       <c r="AO90" s="56"/>
       <c r="AP90" s="58">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ90" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13708,8 +13861,12 @@
         <v>210</v>
       </c>
       <c r="K91" s="56"/>
-      <c r="L91" s="56"/>
-      <c r="M91" s="56"/>
+      <c r="L91" s="56">
+        <v>32.5</v>
+      </c>
+      <c r="M91" s="56">
+        <v>32.200000000000003</v>
+      </c>
       <c r="N91" s="56"/>
       <c r="O91" s="56"/>
       <c r="P91" s="56"/>
@@ -13740,7 +13897,7 @@
       <c r="AO91" s="56"/>
       <c r="AP91" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ91" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13792,7 +13949,9 @@
       <c r="L92" s="56">
         <v>19.3</v>
       </c>
-      <c r="M92" s="56"/>
+      <c r="M92" s="56">
+        <v>18.149999999999999</v>
+      </c>
       <c r="N92" s="56"/>
       <c r="O92" s="56"/>
       <c r="P92" s="56"/>
@@ -13823,7 +13982,7 @@
       <c r="AO92" s="56"/>
       <c r="AP92" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ92" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13875,7 +14034,9 @@
       <c r="L93" s="56">
         <v>25.6</v>
       </c>
-      <c r="M93" s="56"/>
+      <c r="M93" s="56">
+        <v>24.333333333333329</v>
+      </c>
       <c r="N93" s="56"/>
       <c r="O93" s="56"/>
       <c r="P93" s="56"/>
@@ -13906,7 +14067,7 @@
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ93" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13958,7 +14119,9 @@
       <c r="L94" s="56">
         <v>17</v>
       </c>
-      <c r="M94" s="56"/>
+      <c r="M94" s="56">
+        <v>17.649999999999999</v>
+      </c>
       <c r="N94" s="56"/>
       <c r="O94" s="56"/>
       <c r="P94" s="56"/>
@@ -13989,7 +14152,7 @@
       <c r="AO94" s="56"/>
       <c r="AP94" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ94" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14041,7 +14204,9 @@
       <c r="L95" s="56">
         <v>14.95</v>
       </c>
-      <c r="M95" s="56"/>
+      <c r="M95" s="56">
+        <v>15.05</v>
+      </c>
       <c r="N95" s="56"/>
       <c r="O95" s="56"/>
       <c r="P95" s="56"/>
@@ -14072,7 +14237,7 @@
       <c r="AO95" s="56"/>
       <c r="AP95" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ95" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14282,7 +14447,9 @@
       <c r="L98" s="56">
         <v>10.8</v>
       </c>
-      <c r="M98" s="56"/>
+      <c r="M98" s="56">
+        <v>11.75</v>
+      </c>
       <c r="N98" s="56"/>
       <c r="O98" s="56"/>
       <c r="P98" s="56"/>
@@ -14313,7 +14480,7 @@
       <c r="AO98" s="56"/>
       <c r="AP98" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ98" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14365,7 +14532,9 @@
       <c r="L99" s="56">
         <v>14.2</v>
       </c>
-      <c r="M99" s="56"/>
+      <c r="M99" s="56">
+        <v>15.9</v>
+      </c>
       <c r="N99" s="56"/>
       <c r="O99" s="56"/>
       <c r="P99" s="56"/>
@@ -14396,7 +14565,7 @@
       <c r="AO99" s="56"/>
       <c r="AP99" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ99" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14448,7 +14617,9 @@
       <c r="L100" s="56">
         <v>14.66666666666667</v>
       </c>
-      <c r="M100" s="56"/>
+      <c r="M100" s="56">
+        <v>14.266666666666669</v>
+      </c>
       <c r="N100" s="56"/>
       <c r="O100" s="56"/>
       <c r="P100" s="56"/>
@@ -14479,7 +14650,7 @@
       <c r="AO100" s="56"/>
       <c r="AP100" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ100" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14531,7 +14702,9 @@
       <c r="L101" s="56">
         <v>12.85</v>
       </c>
-      <c r="M101" s="56"/>
+      <c r="M101" s="56">
+        <v>12.95</v>
+      </c>
       <c r="N101" s="56"/>
       <c r="O101" s="56"/>
       <c r="P101" s="56"/>
@@ -14562,7 +14735,7 @@
       <c r="AO101" s="56"/>
       <c r="AP101" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ101" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14614,7 +14787,9 @@
       <c r="L102" s="56">
         <v>12.8</v>
       </c>
-      <c r="M102" s="56"/>
+      <c r="M102" s="56">
+        <v>13.53333333333333</v>
+      </c>
       <c r="N102" s="56"/>
       <c r="O102" s="56"/>
       <c r="P102" s="56"/>
@@ -14645,7 +14820,7 @@
       <c r="AO102" s="56"/>
       <c r="AP102" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ102" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14855,7 +15030,9 @@
       <c r="L105" s="56">
         <v>19</v>
       </c>
-      <c r="M105" s="56"/>
+      <c r="M105" s="56">
+        <v>20</v>
+      </c>
       <c r="N105" s="56"/>
       <c r="O105" s="56"/>
       <c r="P105" s="56"/>
@@ -14886,7 +15063,7 @@
       <c r="AO105" s="56"/>
       <c r="AP105" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ105" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15013,7 +15190,9 @@
       </c>
       <c r="K107" s="56"/>
       <c r="L107" s="56"/>
-      <c r="M107" s="56"/>
+      <c r="M107" s="56">
+        <v>15.266666666666669</v>
+      </c>
       <c r="N107" s="56"/>
       <c r="O107" s="56"/>
       <c r="P107" s="56"/>
@@ -15044,7 +15223,7 @@
       <c r="AO107" s="56"/>
       <c r="AP107" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ107" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15096,7 +15275,9 @@
       <c r="L108" s="56">
         <v>13.05</v>
       </c>
-      <c r="M108" s="56"/>
+      <c r="M108" s="56">
+        <v>13.75</v>
+      </c>
       <c r="N108" s="56"/>
       <c r="O108" s="56"/>
       <c r="P108" s="56"/>
@@ -15127,7 +15308,7 @@
       <c r="AO108" s="56"/>
       <c r="AP108" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ108" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15179,7 +15360,9 @@
       <c r="L109" s="56">
         <v>15.05</v>
       </c>
-      <c r="M109" s="56"/>
+      <c r="M109" s="56">
+        <v>14.2</v>
+      </c>
       <c r="N109" s="56"/>
       <c r="O109" s="56"/>
       <c r="P109" s="56"/>
@@ -15210,7 +15393,7 @@
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ109" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15258,7 +15441,9 @@
       </c>
       <c r="K110" s="56"/>
       <c r="L110" s="56"/>
-      <c r="M110" s="56"/>
+      <c r="M110" s="56">
+        <v>16.399999999999999</v>
+      </c>
       <c r="N110" s="56"/>
       <c r="O110" s="56"/>
       <c r="P110" s="56"/>
@@ -15289,7 +15474,7 @@
       <c r="AO110" s="56"/>
       <c r="AP110" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ110" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15341,7 +15526,9 @@
       <c r="L111" s="56">
         <v>15.133333333333329</v>
       </c>
-      <c r="M111" s="56"/>
+      <c r="M111" s="56">
+        <v>14.866666666666671</v>
+      </c>
       <c r="N111" s="56"/>
       <c r="O111" s="56"/>
       <c r="P111" s="56"/>
@@ -15372,7 +15559,7 @@
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ111" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15424,7 +15611,9 @@
       <c r="L112" s="56">
         <v>18.266666666666669</v>
       </c>
-      <c r="M112" s="56"/>
+      <c r="M112" s="56">
+        <v>16.666666666666671</v>
+      </c>
       <c r="N112" s="56"/>
       <c r="O112" s="56"/>
       <c r="P112" s="56"/>
@@ -15455,7 +15644,7 @@
       <c r="AO112" s="56"/>
       <c r="AP112" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ112" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15507,7 +15696,9 @@
       <c r="L113" s="56">
         <v>20.266666666666669</v>
       </c>
-      <c r="M113" s="56"/>
+      <c r="M113" s="56">
+        <v>18.466666666666669</v>
+      </c>
       <c r="N113" s="56"/>
       <c r="O113" s="56"/>
       <c r="P113" s="56"/>
@@ -15538,7 +15729,7 @@
       <c r="AO113" s="56"/>
       <c r="AP113" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ113" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15590,7 +15781,9 @@
       <c r="L114" s="56">
         <v>24.86666666666666</v>
       </c>
-      <c r="M114" s="56"/>
+      <c r="M114" s="56">
+        <v>21</v>
+      </c>
       <c r="N114" s="56"/>
       <c r="O114" s="56"/>
       <c r="P114" s="56"/>
@@ -15621,7 +15814,7 @@
       <c r="AO114" s="56"/>
       <c r="AP114" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ114" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15673,7 +15866,9 @@
       <c r="L115" s="56">
         <v>29.05</v>
       </c>
-      <c r="M115" s="56"/>
+      <c r="M115" s="56">
+        <v>26.75</v>
+      </c>
       <c r="N115" s="56"/>
       <c r="O115" s="56"/>
       <c r="P115" s="56"/>
@@ -15704,7 +15899,7 @@
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ115" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15756,7 +15951,9 @@
       <c r="L116" s="56">
         <v>19.86666666666666</v>
       </c>
-      <c r="M116" s="56"/>
+      <c r="M116" s="56">
+        <v>19.733333333333331</v>
+      </c>
       <c r="N116" s="56"/>
       <c r="O116" s="56"/>
       <c r="P116" s="56"/>
@@ -15787,7 +15984,7 @@
       <c r="AO116" s="56"/>
       <c r="AP116" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ116" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15839,7 +16036,9 @@
       <c r="L117" s="56">
         <v>29.13333333333334</v>
       </c>
-      <c r="M117" s="56"/>
+      <c r="M117" s="56">
+        <v>26.733333333333331</v>
+      </c>
       <c r="N117" s="56"/>
       <c r="O117" s="56"/>
       <c r="P117" s="56"/>
@@ -15870,7 +16069,7 @@
       <c r="AO117" s="56"/>
       <c r="AP117" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ117" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15922,7 +16121,9 @@
       <c r="L118" s="56">
         <v>31</v>
       </c>
-      <c r="M118" s="56"/>
+      <c r="M118" s="56">
+        <v>29.86666666666666</v>
+      </c>
       <c r="N118" s="56"/>
       <c r="O118" s="56"/>
       <c r="P118" s="56"/>
@@ -15953,7 +16154,7 @@
       <c r="AO118" s="56"/>
       <c r="AP118" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ118" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16005,7 +16206,9 @@
       <c r="L119" s="56">
         <v>22.93333333333333</v>
       </c>
-      <c r="M119" s="56"/>
+      <c r="M119" s="56">
+        <v>24.066666666666659</v>
+      </c>
       <c r="N119" s="56"/>
       <c r="O119" s="56"/>
       <c r="P119" s="56"/>
@@ -16036,7 +16239,7 @@
       <c r="AO119" s="56"/>
       <c r="AP119" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ119" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16088,7 +16291,9 @@
       <c r="L120" s="56">
         <v>28.466666666666669</v>
       </c>
-      <c r="M120" s="56"/>
+      <c r="M120" s="56">
+        <v>26.266666666666669</v>
+      </c>
       <c r="N120" s="56"/>
       <c r="O120" s="56"/>
       <c r="P120" s="56"/>
@@ -16119,7 +16324,7 @@
       <c r="AO120" s="56"/>
       <c r="AP120" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ120" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16250,7 +16455,9 @@
       <c r="L122" s="56">
         <v>13.4</v>
       </c>
-      <c r="M122" s="56"/>
+      <c r="M122" s="56">
+        <v>12.266666666666669</v>
+      </c>
       <c r="N122" s="56"/>
       <c r="O122" s="56"/>
       <c r="P122" s="56"/>
@@ -16281,7 +16488,7 @@
       <c r="AO122" s="56"/>
       <c r="AP122" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ122" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16408,7 +16615,9 @@
       </c>
       <c r="K124" s="56"/>
       <c r="L124" s="56"/>
-      <c r="M124" s="56"/>
+      <c r="M124" s="56">
+        <v>16.06666666666667</v>
+      </c>
       <c r="N124" s="56"/>
       <c r="O124" s="56"/>
       <c r="P124" s="56"/>
@@ -16439,7 +16648,7 @@
       <c r="AO124" s="56"/>
       <c r="AP124" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ124" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16566,7 +16775,9 @@
       </c>
       <c r="K126" s="56"/>
       <c r="L126" s="56"/>
-      <c r="M126" s="56"/>
+      <c r="M126" s="56">
+        <v>11.133333333333329</v>
+      </c>
       <c r="N126" s="56"/>
       <c r="O126" s="56"/>
       <c r="P126" s="56"/>
@@ -16597,7 +16808,7 @@
       <c r="AO126" s="56"/>
       <c r="AP126" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ126" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16969,7 +17180,9 @@
       <c r="L131" s="56">
         <v>18.850000000000001</v>
       </c>
-      <c r="M131" s="56"/>
+      <c r="M131" s="56">
+        <v>17.649999999999999</v>
+      </c>
       <c r="N131" s="56"/>
       <c r="O131" s="56"/>
       <c r="P131" s="56"/>
@@ -17000,7 +17213,7 @@
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ131" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17131,7 +17344,9 @@
       <c r="L133" s="56">
         <v>13.66666666666667</v>
       </c>
-      <c r="M133" s="56"/>
+      <c r="M133" s="56">
+        <v>13.03333333333333</v>
+      </c>
       <c r="N133" s="56"/>
       <c r="O133" s="56"/>
       <c r="P133" s="56"/>
@@ -17162,7 +17377,7 @@
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ133" s="71" t="str">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
@@ -17214,7 +17429,9 @@
       <c r="L134" s="56">
         <v>17.333333333333329</v>
       </c>
-      <c r="M134" s="56"/>
+      <c r="M134" s="56">
+        <v>17.333333333333329</v>
+      </c>
       <c r="N134" s="56"/>
       <c r="O134" s="56"/>
       <c r="P134" s="56"/>
@@ -17245,7 +17462,7 @@
       <c r="AO134" s="56"/>
       <c r="AP134" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ134" s="71" t="str">
         <f t="shared" si="7"/>
@@ -17297,7 +17514,9 @@
       <c r="L135" s="56">
         <v>22.65</v>
       </c>
-      <c r="M135" s="56"/>
+      <c r="M135" s="56">
+        <v>21.65</v>
+      </c>
       <c r="N135" s="56"/>
       <c r="O135" s="56"/>
       <c r="P135" s="56"/>
@@ -17328,7 +17547,7 @@
       <c r="AO135" s="56"/>
       <c r="AP135" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ135" s="71" t="str">
         <f t="shared" si="7"/>
@@ -17380,7 +17599,9 @@
       <c r="L136" s="56">
         <v>11.2</v>
       </c>
-      <c r="M136" s="56"/>
+      <c r="M136" s="56">
+        <v>11.06666666666667</v>
+      </c>
       <c r="N136" s="56"/>
       <c r="O136" s="56"/>
       <c r="P136" s="56"/>
@@ -17411,7 +17632,7 @@
       <c r="AO136" s="56"/>
       <c r="AP136" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ136" s="71" t="str">
         <f t="shared" si="7"/>
@@ -17542,7 +17763,9 @@
       <c r="L138" s="56">
         <v>24</v>
       </c>
-      <c r="M138" s="56"/>
+      <c r="M138" s="56">
+        <v>21.6</v>
+      </c>
       <c r="N138" s="56"/>
       <c r="O138" s="56"/>
       <c r="P138" s="56"/>
@@ -17573,7 +17796,7 @@
       <c r="AO138" s="56"/>
       <c r="AP138" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ138" s="71" t="str">
         <f t="shared" si="7"/>
@@ -17625,7 +17848,9 @@
       <c r="L139" s="56">
         <v>13.55</v>
       </c>
-      <c r="M139" s="56"/>
+      <c r="M139" s="56">
+        <v>13.05</v>
+      </c>
       <c r="N139" s="56"/>
       <c r="O139" s="56"/>
       <c r="P139" s="56"/>
@@ -17656,7 +17881,7 @@
       <c r="AO139" s="56"/>
       <c r="AP139" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ139" s="71" t="str">
         <f t="shared" si="7"/>
@@ -17708,7 +17933,9 @@
       <c r="L140" s="56">
         <v>16.100000000000001</v>
       </c>
-      <c r="M140" s="56"/>
+      <c r="M140" s="56">
+        <v>15.55</v>
+      </c>
       <c r="N140" s="56"/>
       <c r="O140" s="56"/>
       <c r="P140" s="56"/>
@@ -17739,7 +17966,7 @@
       <c r="AO140" s="56"/>
       <c r="AP140" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ140" s="71" t="str">
         <f t="shared" si="7"/>
@@ -17791,7 +18018,9 @@
       <c r="L141" s="56">
         <v>13.733333333333331</v>
       </c>
-      <c r="M141" s="56"/>
+      <c r="M141" s="56">
+        <v>12.266666666666669</v>
+      </c>
       <c r="N141" s="56"/>
       <c r="O141" s="56"/>
       <c r="P141" s="56"/>
@@ -17822,7 +18051,7 @@
       <c r="AO141" s="56"/>
       <c r="AP141" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ141" s="71" t="str">
         <f t="shared" si="7"/>
@@ -17874,7 +18103,9 @@
       <c r="L142" s="56">
         <v>10.85</v>
       </c>
-      <c r="M142" s="56"/>
+      <c r="M142" s="56">
+        <v>11.35</v>
+      </c>
       <c r="N142" s="56"/>
       <c r="O142" s="56"/>
       <c r="P142" s="56"/>
@@ -17905,7 +18136,7 @@
       <c r="AO142" s="56"/>
       <c r="AP142" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ142" s="71" t="str">
         <f t="shared" si="7"/>
@@ -17957,7 +18188,9 @@
       <c r="L143" s="56">
         <v>28.8</v>
       </c>
-      <c r="M143" s="56"/>
+      <c r="M143" s="56">
+        <v>27.666666666666671</v>
+      </c>
       <c r="N143" s="56"/>
       <c r="O143" s="56"/>
       <c r="P143" s="56"/>
@@ -17988,7 +18221,7 @@
       <c r="AO143" s="56"/>
       <c r="AP143" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ143" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18040,7 +18273,9 @@
       <c r="L144" s="56">
         <v>14.8</v>
       </c>
-      <c r="M144" s="56"/>
+      <c r="M144" s="56">
+        <v>16.86666666666666</v>
+      </c>
       <c r="N144" s="56"/>
       <c r="O144" s="56"/>
       <c r="P144" s="56"/>
@@ -18071,7 +18306,7 @@
       <c r="AO144" s="56"/>
       <c r="AP144" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ144" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18123,7 +18358,9 @@
       <c r="L145" s="56">
         <v>21</v>
       </c>
-      <c r="M145" s="56"/>
+      <c r="M145" s="56">
+        <v>20.399999999999999</v>
+      </c>
       <c r="N145" s="56"/>
       <c r="O145" s="56"/>
       <c r="P145" s="56"/>
@@ -18154,7 +18391,7 @@
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ145" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18202,7 +18439,9 @@
       </c>
       <c r="K146" s="56"/>
       <c r="L146" s="56"/>
-      <c r="M146" s="56"/>
+      <c r="M146" s="56">
+        <v>31.6</v>
+      </c>
       <c r="N146" s="56"/>
       <c r="O146" s="56"/>
       <c r="P146" s="56"/>
@@ -18233,7 +18472,7 @@
       <c r="AO146" s="56"/>
       <c r="AP146" s="58">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ146" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18285,7 +18524,9 @@
       <c r="L147" s="56">
         <v>26.733333333333331</v>
       </c>
-      <c r="M147" s="56"/>
+      <c r="M147" s="56">
+        <v>25.6</v>
+      </c>
       <c r="N147" s="56"/>
       <c r="O147" s="56"/>
       <c r="P147" s="56"/>
@@ -18316,7 +18557,7 @@
       <c r="AO147" s="56"/>
       <c r="AP147" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ147" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18368,7 +18609,9 @@
       <c r="L148" s="56">
         <v>31.4</v>
       </c>
-      <c r="M148" s="56"/>
+      <c r="M148" s="56">
+        <v>30.6</v>
+      </c>
       <c r="N148" s="56"/>
       <c r="O148" s="56"/>
       <c r="P148" s="56"/>
@@ -18399,7 +18642,7 @@
       <c r="AO148" s="56"/>
       <c r="AP148" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ148" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18451,7 +18694,9 @@
       <c r="L149" s="56">
         <v>24.13333333333334</v>
       </c>
-      <c r="M149" s="56"/>
+      <c r="M149" s="56">
+        <v>23.2</v>
+      </c>
       <c r="N149" s="56"/>
       <c r="O149" s="56"/>
       <c r="P149" s="56"/>
@@ -18482,7 +18727,7 @@
       <c r="AO149" s="56"/>
       <c r="AP149" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ149" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18609,7 +18854,9 @@
       </c>
       <c r="K151" s="56"/>
       <c r="L151" s="56"/>
-      <c r="M151" s="56"/>
+      <c r="M151" s="56">
+        <v>23.8</v>
+      </c>
       <c r="N151" s="56"/>
       <c r="O151" s="56"/>
       <c r="P151" s="56"/>
@@ -18640,7 +18887,7 @@
       <c r="AO151" s="56"/>
       <c r="AP151" s="58">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ151" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18850,7 +19097,9 @@
       <c r="L154" s="56">
         <v>21.55</v>
       </c>
-      <c r="M154" s="56"/>
+      <c r="M154" s="56">
+        <v>21.15</v>
+      </c>
       <c r="N154" s="56"/>
       <c r="O154" s="56"/>
       <c r="P154" s="56"/>
@@ -18881,7 +19130,7 @@
       <c r="AO154" s="56"/>
       <c r="AP154" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ154" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18931,7 +19180,9 @@
       <c r="L155" s="56">
         <v>29.4</v>
       </c>
-      <c r="M155" s="56"/>
+      <c r="M155" s="56">
+        <v>29.733333333333331</v>
+      </c>
       <c r="N155" s="56"/>
       <c r="O155" s="56"/>
       <c r="P155" s="56"/>
@@ -18962,7 +19213,7 @@
       <c r="AO155" s="56"/>
       <c r="AP155" s="58">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ155" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19089,7 +19340,9 @@
       </c>
       <c r="K157" s="56"/>
       <c r="L157" s="56"/>
-      <c r="M157" s="56"/>
+      <c r="M157" s="56">
+        <v>30.06666666666667</v>
+      </c>
       <c r="N157" s="56"/>
       <c r="O157" s="56"/>
       <c r="P157" s="56"/>
@@ -19120,7 +19373,7 @@
       <c r="AO157" s="56"/>
       <c r="AP157" s="58">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ157" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19172,7 +19425,9 @@
       <c r="L158" s="56">
         <v>32</v>
       </c>
-      <c r="M158" s="56"/>
+      <c r="M158" s="56">
+        <v>30.6</v>
+      </c>
       <c r="N158" s="56"/>
       <c r="O158" s="56"/>
       <c r="P158" s="56"/>
@@ -19203,7 +19458,7 @@
       <c r="AO158" s="56"/>
       <c r="AP158" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ158" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19255,7 +19510,9 @@
       <c r="L159" s="56">
         <v>21.533333333333331</v>
       </c>
-      <c r="M159" s="56"/>
+      <c r="M159" s="56">
+        <v>21.4</v>
+      </c>
       <c r="N159" s="56"/>
       <c r="O159" s="56"/>
       <c r="P159" s="56"/>
@@ -19286,7 +19543,7 @@
       <c r="AO159" s="56"/>
       <c r="AP159" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ159" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19338,7 +19595,9 @@
       <c r="L160" s="56">
         <v>28.86666666666666</v>
       </c>
-      <c r="M160" s="56"/>
+      <c r="M160" s="56">
+        <v>27.4</v>
+      </c>
       <c r="N160" s="56"/>
       <c r="O160" s="56"/>
       <c r="P160" s="56"/>
@@ -19369,7 +19628,7 @@
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ160" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19421,7 +19680,9 @@
       <c r="L161" s="56">
         <v>20</v>
       </c>
-      <c r="M161" s="56"/>
+      <c r="M161" s="56">
+        <v>20.266666666666669</v>
+      </c>
       <c r="N161" s="56"/>
       <c r="O161" s="56"/>
       <c r="P161" s="56"/>
@@ -19452,7 +19713,7 @@
       <c r="AO161" s="56"/>
       <c r="AP161" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ161" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19504,7 +19765,9 @@
       <c r="L162" s="56">
         <v>29.966666666666669</v>
       </c>
-      <c r="M162" s="56"/>
+      <c r="M162" s="56">
+        <v>29.2</v>
+      </c>
       <c r="N162" s="56"/>
       <c r="O162" s="56"/>
       <c r="P162" s="56"/>
@@ -19535,7 +19798,7 @@
       <c r="AO162" s="56"/>
       <c r="AP162" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ162" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19587,7 +19850,9 @@
       <c r="L163" s="56">
         <v>21.666666666666671</v>
       </c>
-      <c r="M163" s="56"/>
+      <c r="M163" s="56">
+        <v>21.2</v>
+      </c>
       <c r="N163" s="56"/>
       <c r="O163" s="56"/>
       <c r="P163" s="56"/>
@@ -19618,7 +19883,7 @@
       <c r="AO163" s="56"/>
       <c r="AP163" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ163" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19913,7 +20178,9 @@
       <c r="L167" s="56">
         <v>22.06666666666667</v>
       </c>
-      <c r="M167" s="56"/>
+      <c r="M167" s="56">
+        <v>21.6</v>
+      </c>
       <c r="N167" s="56"/>
       <c r="O167" s="56"/>
       <c r="P167" s="56"/>
@@ -19944,7 +20211,7 @@
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ167" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19996,7 +20263,9 @@
       <c r="L168" s="56">
         <v>29.75</v>
       </c>
-      <c r="M168" s="56"/>
+      <c r="M168" s="56">
+        <v>28.1</v>
+      </c>
       <c r="N168" s="56"/>
       <c r="O168" s="56"/>
       <c r="P168" s="56"/>
@@ -20027,7 +20296,7 @@
       <c r="AO168" s="56"/>
       <c r="AP168" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ168" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20079,7 +20348,9 @@
       <c r="L169" s="56">
         <v>9.4</v>
       </c>
-      <c r="M169" s="56"/>
+      <c r="M169" s="56">
+        <v>9.65</v>
+      </c>
       <c r="N169" s="56"/>
       <c r="O169" s="56"/>
       <c r="P169" s="56"/>
@@ -20110,7 +20381,7 @@
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ169" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20162,7 +20433,9 @@
       <c r="L170" s="56">
         <v>27.6</v>
       </c>
-      <c r="M170" s="56"/>
+      <c r="M170" s="56">
+        <v>24.733333333333331</v>
+      </c>
       <c r="N170" s="56"/>
       <c r="O170" s="56"/>
       <c r="P170" s="56"/>
@@ -20193,7 +20466,7 @@
       <c r="AO170" s="56"/>
       <c r="AP170" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ170" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20245,7 +20518,9 @@
       <c r="L171" s="56">
         <v>22</v>
       </c>
-      <c r="M171" s="56"/>
+      <c r="M171" s="56">
+        <v>20.6</v>
+      </c>
       <c r="N171" s="56"/>
       <c r="O171" s="56"/>
       <c r="P171" s="56"/>
@@ -20276,7 +20551,7 @@
       <c r="AO171" s="56"/>
       <c r="AP171" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ171" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20326,7 +20601,9 @@
         <v>25.85</v>
       </c>
       <c r="L172" s="56"/>
-      <c r="M172" s="56"/>
+      <c r="M172" s="56">
+        <v>25.45</v>
+      </c>
       <c r="N172" s="56"/>
       <c r="O172" s="56"/>
       <c r="P172" s="56"/>
@@ -20357,7 +20634,7 @@
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ172" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20409,7 +20686,9 @@
       <c r="L173" s="56">
         <v>25.9</v>
       </c>
-      <c r="M173" s="56"/>
+      <c r="M173" s="56">
+        <v>24.55</v>
+      </c>
       <c r="N173" s="56"/>
       <c r="O173" s="56"/>
       <c r="P173" s="56"/>
@@ -20440,7 +20719,7 @@
       <c r="AO173" s="56"/>
       <c r="AP173" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ173" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20492,7 +20771,9 @@
       <c r="L174" s="56">
         <v>15.4</v>
       </c>
-      <c r="M174" s="56"/>
+      <c r="M174" s="56">
+        <v>12.66666666666667</v>
+      </c>
       <c r="N174" s="56"/>
       <c r="O174" s="56"/>
       <c r="P174" s="56"/>
@@ -20523,7 +20804,7 @@
       <c r="AO174" s="56"/>
       <c r="AP174" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ174" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20816,7 +21097,9 @@
       <c r="L178" s="56">
         <v>26.533333333333331</v>
       </c>
-      <c r="M178" s="56"/>
+      <c r="M178" s="56">
+        <v>24.933333333333341</v>
+      </c>
       <c r="N178" s="56"/>
       <c r="O178" s="56"/>
       <c r="P178" s="56"/>
@@ -20847,7 +21130,7 @@
       <c r="AO178" s="56"/>
       <c r="AP178" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ178" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20899,7 +21182,9 @@
       <c r="L179" s="56">
         <v>19.05</v>
       </c>
-      <c r="M179" s="56"/>
+      <c r="M179" s="56">
+        <v>18.850000000000001</v>
+      </c>
       <c r="N179" s="56"/>
       <c r="O179" s="56"/>
       <c r="P179" s="56"/>
@@ -20930,7 +21215,7 @@
       <c r="AO179" s="56"/>
       <c r="AP179" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ179" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21061,7 +21346,9 @@
       <c r="L181" s="56">
         <v>31.86666666666666</v>
       </c>
-      <c r="M181" s="56"/>
+      <c r="M181" s="56">
+        <v>31.4</v>
+      </c>
       <c r="N181" s="56"/>
       <c r="O181" s="56"/>
       <c r="P181" s="56"/>
@@ -21092,7 +21379,7 @@
       <c r="AO181" s="56"/>
       <c r="AP181" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ181" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21302,7 +21589,9 @@
       <c r="L184" s="56">
         <v>29.2</v>
       </c>
-      <c r="M184" s="56"/>
+      <c r="M184" s="56">
+        <v>29.266666666666669</v>
+      </c>
       <c r="N184" s="56"/>
       <c r="O184" s="56"/>
       <c r="P184" s="56"/>
@@ -21333,7 +21622,7 @@
       <c r="AO184" s="56"/>
       <c r="AP184" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ184" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21385,7 +21674,9 @@
       <c r="L185" s="56">
         <v>30.733333333333331</v>
       </c>
-      <c r="M185" s="56"/>
+      <c r="M185" s="56">
+        <v>30.666666666666671</v>
+      </c>
       <c r="N185" s="56"/>
       <c r="O185" s="56"/>
       <c r="P185" s="56"/>
@@ -21416,7 +21707,7 @@
       <c r="AO185" s="56"/>
       <c r="AP185" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ185" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21624,7 +21915,9 @@
         <v>18.93333333333333</v>
       </c>
       <c r="L188" s="56"/>
-      <c r="M188" s="56"/>
+      <c r="M188" s="56">
+        <v>17.533333333333331</v>
+      </c>
       <c r="N188" s="56"/>
       <c r="O188" s="56"/>
       <c r="P188" s="56"/>
@@ -21655,7 +21948,7 @@
       <c r="AO188" s="56"/>
       <c r="AP188" s="58">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ188" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21705,7 +21998,9 @@
         <v>33.200000000000003</v>
       </c>
       <c r="L189" s="56"/>
-      <c r="M189" s="56"/>
+      <c r="M189" s="56">
+        <v>32.799999999999997</v>
+      </c>
       <c r="N189" s="56"/>
       <c r="O189" s="56"/>
       <c r="P189" s="56"/>
@@ -21736,7 +22031,7 @@
       <c r="AO189" s="56"/>
       <c r="AP189" s="58">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ189" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21788,7 +22083,9 @@
       <c r="L190" s="56">
         <v>31.466666666666669</v>
       </c>
-      <c r="M190" s="56"/>
+      <c r="M190" s="56">
+        <v>29.733333333333331</v>
+      </c>
       <c r="N190" s="56"/>
       <c r="O190" s="56"/>
       <c r="P190" s="56"/>
@@ -21819,7 +22116,7 @@
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ190" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21871,7 +22168,9 @@
       <c r="L191" s="56">
         <v>18.95</v>
       </c>
-      <c r="M191" s="56"/>
+      <c r="M191" s="56">
+        <v>18.95</v>
+      </c>
       <c r="N191" s="56"/>
       <c r="O191" s="56"/>
       <c r="P191" s="56"/>
@@ -21902,7 +22201,7 @@
       <c r="AO191" s="56"/>
       <c r="AP191" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ191" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21954,7 +22253,9 @@
       <c r="L192" s="56">
         <v>26.4</v>
       </c>
-      <c r="M192" s="56"/>
+      <c r="M192" s="56">
+        <v>28.06666666666667</v>
+      </c>
       <c r="N192" s="56"/>
       <c r="O192" s="56"/>
       <c r="P192" s="56"/>
@@ -21985,7 +22286,7 @@
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ192" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22037,7 +22338,9 @@
       <c r="L193" s="56">
         <v>29.5</v>
       </c>
-      <c r="M193" s="56"/>
+      <c r="M193" s="56">
+        <v>27.6</v>
+      </c>
       <c r="N193" s="56"/>
       <c r="O193" s="56"/>
       <c r="P193" s="56"/>
@@ -22068,7 +22371,7 @@
       <c r="AO193" s="56"/>
       <c r="AP193" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ193" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22120,7 +22423,9 @@
       <c r="L194" s="56">
         <v>22.733333333333331</v>
       </c>
-      <c r="M194" s="56"/>
+      <c r="M194" s="56">
+        <v>22.06666666666667</v>
+      </c>
       <c r="N194" s="56"/>
       <c r="O194" s="56"/>
       <c r="P194" s="56"/>
@@ -22151,7 +22456,7 @@
       <c r="AO194" s="56"/>
       <c r="AP194" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ194" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22203,7 +22508,9 @@
       <c r="L195" s="56">
         <v>30.86666666666666</v>
       </c>
-      <c r="M195" s="56"/>
+      <c r="M195" s="56">
+        <v>27.86666666666666</v>
+      </c>
       <c r="N195" s="56"/>
       <c r="O195" s="56"/>
       <c r="P195" s="56"/>
@@ -22234,7 +22541,7 @@
       <c r="AO195" s="56"/>
       <c r="AP195" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ195" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22286,7 +22593,9 @@
       <c r="L196" s="56">
         <v>24.6</v>
       </c>
-      <c r="M196" s="56"/>
+      <c r="M196" s="56">
+        <v>23.2</v>
+      </c>
       <c r="N196" s="56"/>
       <c r="O196" s="56"/>
       <c r="P196" s="56"/>
@@ -22317,7 +22626,7 @@
       <c r="AO196" s="56"/>
       <c r="AP196" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ196" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22369,7 +22678,9 @@
       <c r="L197" s="56">
         <v>28.6</v>
       </c>
-      <c r="M197" s="56"/>
+      <c r="M197" s="56">
+        <v>27.466666666666669</v>
+      </c>
       <c r="N197" s="56"/>
       <c r="O197" s="56"/>
       <c r="P197" s="56"/>
@@ -22400,7 +22711,7 @@
       <c r="AO197" s="56"/>
       <c r="AP197" s="58">
         <f t="shared" ref="AP197:AP260" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ197" s="71" t="str">
         <f t="shared" ref="AQ197:AQ260" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
@@ -22452,7 +22763,9 @@
       <c r="L198" s="56">
         <v>22.6</v>
       </c>
-      <c r="M198" s="56"/>
+      <c r="M198" s="56">
+        <v>21.95</v>
+      </c>
       <c r="N198" s="56"/>
       <c r="O198" s="56"/>
       <c r="P198" s="56"/>
@@ -22483,7 +22796,7 @@
       <c r="AO198" s="56"/>
       <c r="AP198" s="58">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ198" s="71" t="str">
         <f t="shared" si="10"/>
@@ -22535,7 +22848,9 @@
       <c r="L199" s="56">
         <v>16.866666666666671</v>
       </c>
-      <c r="M199" s="56"/>
+      <c r="M199" s="56">
+        <v>16.600000000000001</v>
+      </c>
       <c r="N199" s="56"/>
       <c r="O199" s="56"/>
       <c r="P199" s="56"/>
@@ -22566,7 +22881,7 @@
       <c r="AO199" s="56"/>
       <c r="AP199" s="58">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ199" s="71" t="str">
         <f t="shared" si="10"/>
@@ -22618,7 +22933,9 @@
       <c r="L200" s="56">
         <v>13.75</v>
       </c>
-      <c r="M200" s="56"/>
+      <c r="M200" s="56">
+        <v>14.25</v>
+      </c>
       <c r="N200" s="56"/>
       <c r="O200" s="56"/>
       <c r="P200" s="56"/>
@@ -22649,7 +22966,7 @@
       <c r="AO200" s="56"/>
       <c r="AP200" s="58">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ200" s="71" t="str">
         <f t="shared" si="10"/>
@@ -22698,8 +23015,12 @@
       <c r="K201" s="56">
         <v>28.3</v>
       </c>
-      <c r="L201" s="56"/>
-      <c r="M201" s="56"/>
+      <c r="L201" s="56">
+        <v>28.9</v>
+      </c>
+      <c r="M201" s="56">
+        <v>27.7</v>
+      </c>
       <c r="N201" s="56"/>
       <c r="O201" s="56"/>
       <c r="P201" s="56"/>
@@ -22730,7 +23051,7 @@
       <c r="AO201" s="56"/>
       <c r="AP201" s="58">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ201" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23023,7 +23344,9 @@
       <c r="L205" s="56">
         <v>13.85</v>
       </c>
-      <c r="M205" s="56"/>
+      <c r="M205" s="56">
+        <v>12.25</v>
+      </c>
       <c r="N205" s="56"/>
       <c r="O205" s="56"/>
       <c r="P205" s="56"/>
@@ -23054,7 +23377,7 @@
       <c r="AO205" s="56"/>
       <c r="AP205" s="58">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ205" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23103,7 +23426,9 @@
       <c r="K206" s="56">
         <v>14.2</v>
       </c>
-      <c r="L206" s="56"/>
+      <c r="L206" s="56">
+        <v>14.8</v>
+      </c>
       <c r="M206" s="56"/>
       <c r="N206" s="56"/>
       <c r="O206" s="56"/>
@@ -23135,7 +23460,7 @@
       <c r="AO206" s="56"/>
       <c r="AP206" s="58">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ206" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23183,7 +23508,9 @@
       </c>
       <c r="K207" s="56"/>
       <c r="L207" s="56"/>
-      <c r="M207" s="56"/>
+      <c r="M207" s="56">
+        <v>13.4</v>
+      </c>
       <c r="N207" s="56"/>
       <c r="O207" s="56"/>
       <c r="P207" s="56"/>
@@ -23214,7 +23541,7 @@
       <c r="AO207" s="56"/>
       <c r="AP207" s="58">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ207" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23266,7 +23593,9 @@
       <c r="L208" s="56">
         <v>13.75</v>
       </c>
-      <c r="M208" s="56"/>
+      <c r="M208" s="56">
+        <v>12.35</v>
+      </c>
       <c r="N208" s="56"/>
       <c r="O208" s="56"/>
       <c r="P208" s="56"/>
@@ -23297,7 +23626,7 @@
       <c r="AO208" s="56"/>
       <c r="AP208" s="58">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ208" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23349,7 +23678,9 @@
       <c r="L209" s="56">
         <v>10.8</v>
       </c>
-      <c r="M209" s="56"/>
+      <c r="M209" s="56">
+        <v>10.5</v>
+      </c>
       <c r="N209" s="56"/>
       <c r="O209" s="56"/>
       <c r="P209" s="56"/>
@@ -23380,7 +23711,7 @@
       <c r="AO209" s="56"/>
       <c r="AP209" s="58">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ209" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23426,9 +23757,15 @@
       <c r="J210" s="60" t="s">
         <v>415</v>
       </c>
-      <c r="K210" s="56"/>
-      <c r="L210" s="56"/>
-      <c r="M210" s="56"/>
+      <c r="K210" s="56">
+        <v>14.8</v>
+      </c>
+      <c r="L210" s="56">
+        <v>14.7</v>
+      </c>
+      <c r="M210" s="56">
+        <v>14.9</v>
+      </c>
       <c r="N210" s="56"/>
       <c r="O210" s="56"/>
       <c r="P210" s="56"/>
@@ -23459,7 +23796,7 @@
       <c r="AO210" s="56"/>
       <c r="AP210" s="58">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AQ210" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23505,9 +23842,15 @@
       <c r="J211" s="60" t="s">
         <v>417</v>
       </c>
-      <c r="K211" s="56"/>
-      <c r="L211" s="56"/>
-      <c r="M211" s="56"/>
+      <c r="K211" s="56">
+        <v>8.4</v>
+      </c>
+      <c r="L211" s="56">
+        <v>8.75</v>
+      </c>
+      <c r="M211" s="56">
+        <v>8.15</v>
+      </c>
       <c r="N211" s="56"/>
       <c r="O211" s="56"/>
       <c r="P211" s="56"/>
@@ -23538,7 +23881,7 @@
       <c r="AO211" s="56"/>
       <c r="AP211" s="58">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AQ211" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23588,7 +23931,9 @@
         <v>27.35</v>
       </c>
       <c r="L212" s="56"/>
-      <c r="M212" s="56"/>
+      <c r="M212" s="56">
+        <v>27.7</v>
+      </c>
       <c r="N212" s="56"/>
       <c r="O212" s="56"/>
       <c r="P212" s="56"/>
@@ -23619,7 +23964,7 @@
       <c r="AO212" s="56"/>
       <c r="AP212" s="58">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ212" s="71" t="str">
         <f t="shared" si="10"/>
